--- a/ig/TEST-SUPPLEMENT/CodeSystem-TRE-R343-FonctionLieu.xlsx
+++ b/ig/TEST-SUPPLEMENT/CodeSystem-TRE-R343-FonctionLieu.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="88">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250620120000</t>
+    <t>20251017120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-20T12:00:00+01:00</t>
+    <t>2025-10-17T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>Code</t>
@@ -269,6 +269,15 @@
   </si>
   <si>
     <t>Salle de travail (salle de naissance)</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>Bloc obstétrical</t>
+  </si>
+  <si>
+    <t>Lieu hospitalier dédié à la prise en charge des césariennes, disposant des locaux, du matériel et des équipes pluridisciplinaires (sages-femmes, obstétriciens, anesthésistes, pédiatres) nécessaires à toute heure pour assurer la sécurité de la mère et du nouveau-né, y compris en cas de complications obstétricales.</t>
   </si>
 </sst>
 </file>
@@ -678,7 +687,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -851,6 +860,20 @@
       </c>
       <c r="D14" s="2"/>
     </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
